--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20211.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -88,7 +88,7 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>ZUÑIGA</t>
@@ -97,19 +97,13 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>OSORIO</t>
+    <t>PANZO</t>
   </si>
   <si>
     <t>ESPINDOLA</t>
@@ -118,37 +112,19 @@
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
     <t>ANETTE JOCELYN</t>
   </si>
   <si>
-    <t>KARINA YOSELIN</t>
+    <t>ADAL</t>
   </si>
   <si>
     <t>ROSA ITZEL</t>
   </si>
   <si>
     <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>VIANEY</t>
-  </si>
-  <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
-    <t>NOEMI</t>
   </si>
 </sst>
 </file>
@@ -549,19 +525,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>82.34999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -627,19 +603,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>74.42</v>
+        <v>83.72</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -653,19 +629,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>81.40000000000001</v>
+        <v>86.05</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -679,19 +655,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -744,16 +720,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>85.29000000000001</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -767,16 +746,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>64.52</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -790,16 +772,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>77.78</v>
+      </c>
+      <c r="H4">
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -813,16 +798,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>72.09</v>
+      </c>
+      <c r="H5">
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -836,16 +824,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>83.72</v>
+      </c>
+      <c r="H6">
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -859,16 +850,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H7">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -921,16 +915,16 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>82.34999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
         <v>8.4</v>
@@ -959,7 +953,7 @@
         <v>74.19</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -985,7 +979,7 @@
         <v>91.67</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -999,19 +993,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>74.42</v>
+        <v>83.72</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1025,19 +1019,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>81.40000000000001</v>
+        <v>86.05</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1051,19 +1045,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1073,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1111,10 +1105,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1123,7 +1117,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1134,10 +1128,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1146,21 +1140,21 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920328</v>
+        <v>21330051920309</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1169,7 +1163,7 @@
         <v>13</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1180,10 +1174,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1192,7 +1186,7 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1203,10 +1197,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1215,76 +1209,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920283</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920311</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920352</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20211.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20211.xlsx
@@ -1117,7 +1117,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1140,7 +1140,7 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1163,7 +1163,7 @@
         <v>13</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1186,7 +1186,7 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1209,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20211.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -82,49 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>PANZO</t>
   </si>
   <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
     <t>ADAL</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
   </si>
 </sst>
 </file>
@@ -525,19 +489,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -551,19 +515,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>74.19</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -577,19 +541,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -603,19 +567,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>83.72</v>
+        <v>90.7</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -629,19 +593,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>86.05</v>
+        <v>88.37</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -655,16 +619,16 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>8.5</v>
@@ -720,19 +684,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>85.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -746,19 +710,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>64.52</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -772,19 +736,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>77.78</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -798,19 +762,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>72.09</v>
+        <v>88.37</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -824,19 +788,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -850,16 +814,16 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>8.5</v>
@@ -915,19 +879,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -941,19 +905,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>74.19</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -967,19 +931,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -993,19 +957,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1019,10 +983,10 @@
         <v>43</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>6</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
       </c>
       <c r="F6">
         <v>37</v>
@@ -1031,7 +995,7 @@
         <v>86.05</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1045,19 +1009,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1099,117 +1063,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920201</v>
+        <v>21330051920309</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920306</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920309</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920330</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920199</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
